--- a/resultados/metricas.xlsx
+++ b/resultados/metricas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/asbonato/mpe-fgv-eesp/_dissertacao/codigo/final/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0948813-DD92-7449-BA8B-A8A45D84AA63}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9F8A7AA-E156-874F-8983-BE631A9B1BA6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2040" yWindow="460" windowWidth="21600" windowHeight="17540" xr2:uid="{D05725FF-DF99-F44E-846D-82DF82A7531E}"/>
+    <workbookView xWindow="2040" yWindow="460" windowWidth="26160" windowHeight="17540" xr2:uid="{D05725FF-DF99-F44E-846D-82DF82A7531E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="H98" s="6"/>
       <c r="I98">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.2">
@@ -3164,10 +3164,10 @@
         <v>15</v>
       </c>
       <c r="B99" s="5">
-        <v>1586597489.5643439</v>
+        <v>1411436552.306663</v>
       </c>
       <c r="C99" s="7">
-        <v>0.1057216332415558</v>
+        <v>9.5877271923958021E-2</v>
       </c>
       <c r="D99" s="3">
         <v>2020</v>
@@ -3179,11 +3179,11 @@
         <v>11</v>
       </c>
       <c r="G99" s="6">
-        <v>-3.5318706400000002</v>
+        <v>-3.6465598300000002</v>
       </c>
       <c r="H99" s="6"/>
       <c r="I99">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.2">
